--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +469,90 @@
       </c>
       <c r="E2" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46233</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46233</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46233</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46233</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,6 +553,27 @@
       </c>
       <c r="E6" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -574,6 +574,69 @@
       </c>
       <c r="E7" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ENEV3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RADL3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,7 +577,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46237</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46237</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46237</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -637,6 +637,27 @@
       </c>
       <c r="E10" t="n">
         <v>63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ALOS3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,7 +640,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -658,6 +658,27 @@
       </c>
       <c r="E11" t="n">
         <v>28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>53.82</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46239</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -678,6 +678,27 @@
         <v>53.82</v>
       </c>
       <c r="E12" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="E13" t="n">
         <v>16</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,7 +682,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>46239</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -699,6 +699,48 @@
         <v>53.48</v>
       </c>
       <c r="E13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.789999961853027</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>53.47999954223633</v>
+      </c>
+      <c r="E15" t="n">
         <v>16</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,7 +703,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -741,6 +741,48 @@
         <v>53.47999954223633</v>
       </c>
       <c r="E15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.789999961853027</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>53.47999954223633</v>
+      </c>
+      <c r="E17" t="n">
         <v>16</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,7 +745,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -783,6 +783,48 @@
         <v>53.47999954223633</v>
       </c>
       <c r="E17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4.789999961853027</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>53.47999954223633</v>
+      </c>
+      <c r="E19" t="n">
         <v>16</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -826,6 +826,90 @@
       </c>
       <c r="E19" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ALOS3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>27</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SUZB3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,7 +829,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -909,6 +909,90 @@
         <v>41.97</v>
       </c>
       <c r="E23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ALOS3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>27</v>
+      </c>
+      <c r="E24" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SUZB3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="E27" t="n">
         <v>11</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,7 +913,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -994,6 +994,153 @@
       </c>
       <c r="E27" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="E28" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BOVA11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="E29" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CMIN3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CXSE3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="E31" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E32" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="E33" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -997,7 +997,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1141,6 +1141,48 @@
       </c>
       <c r="E34" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ENEV3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="E35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,7 +1144,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46244</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46244</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1183,6 +1183,27 @@
       </c>
       <c r="E36" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BPAC11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="E37" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,7 +1186,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46245</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1204,6 +1204,48 @@
       </c>
       <c r="E37" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E38" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RADL3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="E39" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,7 +1207,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1246,6 +1246,48 @@
       </c>
       <c r="E39" t="n">
         <v>63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CMIN3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="E41" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1249,7 +1249,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46251</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>46251</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1288,6 +1288,27 @@
       </c>
       <c r="E41" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HYPE3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="E42" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,7 +1291,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>46252</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1309,6 +1309,69 @@
       </c>
       <c r="E42" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="E44" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SUZB3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,7 +1312,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>46253</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>46253</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>46253</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1372,6 +1372,48 @@
       </c>
       <c r="E45" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EZTC3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RADL3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="E47" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,7 +1375,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1414,6 +1414,69 @@
       </c>
       <c r="E47" t="n">
         <v>63</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E48" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ENEV3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="E50" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -1477,6 +1477,48 @@
       </c>
       <c r="E50" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HYPE3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RDOR3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="E52" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,7 +1480,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -1519,6 +1519,27 @@
       </c>
       <c r="E52" t="n">
         <v>35</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4.710000038146973</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,7 +1522,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46261</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -1539,6 +1539,27 @@
         <v>4.710000038146973</v>
       </c>
       <c r="E53" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="E54" t="n">
         <v>20</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,7 +462,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.57999992370605</v>
+        <v>4.95</v>
       </c>
       <c r="E2" t="n">
         <v>22</v>
@@ -477,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,7 +483,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.95</v>
+        <v>10.57999992370605</v>
       </c>
       <c r="E3" t="n">
         <v>22</v>
@@ -683,11 +680,11 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>ALOS3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -696,10 +693,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53.48</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -708,7 +705,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -717,10 +714,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.789999961853027</v>
+        <v>3.5</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +726,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,10 +735,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53.47999954223633</v>
+        <v>4.789999961853027</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +747,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -759,10 +756,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.789999961853027</v>
+        <v>53.47999954223633</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -771,7 +768,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -780,19 +777,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53.47999954223633</v>
+        <v>41.97</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>ALOS3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -801,19 +798,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4.789999961853027</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -822,19 +819,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.47999954223633</v>
+        <v>20.06</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ALOS3</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -843,19 +840,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>3.5</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -864,19 +861,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3.5</v>
+        <v>169.37</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>CMIN3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -885,19 +882,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4.57</v>
+        <v>5.45</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -906,10 +903,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.97</v>
+        <v>19.32</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -918,7 +915,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ALOS3</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -927,10 +924,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>3.73</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -939,7 +936,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>10.67</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -960,7 +957,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -969,10 +966,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.67</v>
+        <v>40.87</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -981,7 +978,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -990,10 +987,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>41.97</v>
+        <v>57.45</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1002,7 +999,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1011,19 +1008,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20.06</v>
+        <v>41.97</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1032,19 +1029,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>169.37</v>
+        <v>25.32</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CMIN3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1053,19 +1050,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5.45</v>
+        <v>10.64</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CXSE3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1074,15 +1071,15 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.32</v>
+        <v>50.13</v>
       </c>
       <c r="E31" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1091,11 +1088,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.73</v>
+        <v>3.98</v>
       </c>
       <c r="E32" t="n">
         <v>26</v>
@@ -1103,11 +1100,11 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1116,61 +1113,61 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>40.87</v>
+        <v>17.53</v>
       </c>
       <c r="E33" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>CMIN3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>57.45</v>
+        <v>5.78</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25.32</v>
+        <v>4.86</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1179,40 +1176,40 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.64</v>
+        <v>20.72</v>
       </c>
       <c r="E36" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>50.13</v>
+        <v>3.57</v>
       </c>
       <c r="E37" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1221,40 +1218,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3.98</v>
+        <v>4.88</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>17.53</v>
+        <v>43.07</v>
       </c>
       <c r="E39" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CMIN3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1263,19 +1260,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.78</v>
+        <v>11.27</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1284,40 +1281,40 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.86</v>
+        <v>18.43</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20.72</v>
+        <v>5.16</v>
       </c>
       <c r="E42" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1326,19 +1323,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.57</v>
+        <v>26.1</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1347,19 +1344,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.88</v>
+        <v>7.12</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1368,19 +1365,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>43.07</v>
+        <v>21.8</v>
       </c>
       <c r="E45" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1389,19 +1386,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.27</v>
+        <v>36.07</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1410,156 +1407,9 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18.43</v>
+        <v>4.710000038146973</v>
       </c>
       <c r="E47" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CSNA3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="E48" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ENEV3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>USIM5</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="E50" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>HYPE3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E51" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>RDOR3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>36.07</v>
-      </c>
-      <c r="E52" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MGLU3</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4.710000038146973</v>
-      </c>
-      <c r="E53" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MGLU3</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E54" t="n">
         <v>20</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,6 +1416,132 @@
         <v>20</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ALOS3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="E48" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SMAL11</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>106.13</v>
+      </c>
+      <c r="E53" t="n">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -1539,6 +1539,132 @@
         <v>106.13</v>
       </c>
       <c r="E53" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ALOS3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>26.69000053405762</v>
+      </c>
+      <c r="E54" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.6600000262260437</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.89999961853027</v>
+      </c>
+      <c r="E56" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>62.68000030517578</v>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>49.08000183105469</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SMAL11</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>106.129997253418</v>
+      </c>
+      <c r="E59" t="n">
         <v>31</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,7 +1543,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -1666,6 +1666,48 @@
       </c>
       <c r="E59" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>20.17000007629395</v>
+      </c>
+      <c r="E60" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>60.54000091552734</v>
+      </c>
+      <c r="E61" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1669,7 +1669,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -1708,6 +1708,27 @@
       </c>
       <c r="E61" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MOVI3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>7.849999904632568</v>
+      </c>
+      <c r="E62" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1711,7 +1711,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46267</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -1729,6 +1729,27 @@
       </c>
       <c r="E62" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>60.22999954223633</v>
+      </c>
+      <c r="E63" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,7 +1732,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -1749,6 +1749,27 @@
         <v>60.22999954223633</v>
       </c>
       <c r="E63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>60.18999862670898</v>
+      </c>
+      <c r="E64" t="n">
         <v>8</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1753,7 +1753,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46272</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -1771,6 +1771,27 @@
       </c>
       <c r="E64" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CXSE3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>20.20999908447266</v>
+      </c>
+      <c r="E65" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1774,7 +1774,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>46273</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -1792,6 +1792,27 @@
       </c>
       <c r="E65" t="n">
         <v>49</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>64.23999786376953</v>
+      </c>
+      <c r="E66" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
